--- a/ABA_mining/outputs/eval/task3/staff/llama3.2/zero_shot/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/staff/llama3.2/zero_shot/Contrary(P)Body(N).xlsx
@@ -33651,13 +33651,13 @@
         <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3768996960486322</v>
+        <v>0.3769</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8104575163398693</v>
+        <v>0.810458</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5145228215767635</v>
+        <v>0.514523</v>
       </c>
       <c r="O2" t="n">
         <v>0.532</v>
@@ -33710,13 +33710,13 @@
         <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3723723723723724</v>
+        <v>0.372372</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8104575163398693</v>
+        <v>0.810458</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5102880658436214</v>
+        <v>0.510288</v>
       </c>
       <c r="O3" t="n">
         <v>0.524</v>
@@ -33769,13 +33769,13 @@
         <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3716012084592145</v>
+        <v>0.371601</v>
       </c>
       <c r="M4" t="n">
-        <v>0.803921568627451</v>
+        <v>0.803922</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5082644628099173</v>
+        <v>0.508264</v>
       </c>
       <c r="O4" t="n">
         <v>0.524</v>
